--- a/data/Apply_Leave_Test_Data.xlsx
+++ b/data/Apply_Leave_Test_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ppham\Documents\Do an\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7118A2-0B0E-4866-BEC4-5B7AE111C89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE8F88D-DA1F-4F9B-8CEB-4DCFDDF26248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3516" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Apply_Leave_Data" sheetId="1" r:id="rId1"/>
@@ -487,200 +487,200 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:I9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="11" style="5" customWidth="1"/>
-    <col min="5" max="5" width="11.21875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="51.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="11" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" customWidth="1"/>
+    <col min="8" max="8" width="51.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="4">
+        <v>46143</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46144</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="C3" s="4">
+        <v>46174</v>
+      </c>
       <c r="D3" s="4">
-        <v>46143</v>
-      </c>
-      <c r="E3" s="4">
-        <v>46144</v>
-      </c>
-      <c r="F3" s="4" t="s">
+        <v>46203</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>24</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4">
+        <v>46152</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46152</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4">
-        <v>46174</v>
-      </c>
-      <c r="E4" s="4">
-        <v>46203</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="C5" s="4">
+        <v>46152</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46147</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="4">
-        <v>46152</v>
-      </c>
-      <c r="E5" s="4">
-        <v>46152</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="H5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="4">
-        <v>46152</v>
-      </c>
-      <c r="E6" s="4">
-        <v>46147</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="H7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="4">
+        <v>46147</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46143</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="4">
-        <v>46147</v>
-      </c>
-      <c r="E9" s="4">
-        <v>46143</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="2" t="s">
         <v>26</v>
       </c>
     </row>
